--- a/Result/profitability/1905.xlsx
+++ b/Result/profitability/1905.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0575</v>
+        <v>-0.11125</v>
       </c>
       <c r="N2" t="n">
-        <v>6.36875</v>
+        <v>5.220000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02</v>
+        <v>-0.04375</v>
       </c>
       <c r="N3" t="n">
-        <v>7.350000000000001</v>
+        <v>6.875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01625</v>
+        <v>0.01</v>
       </c>
       <c r="N4" t="n">
-        <v>8.44875</v>
+        <v>8.16375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.67</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02875</v>
+        <v>-0.0425</v>
       </c>
       <c r="N5" t="n">
-        <v>3.432500000000001</v>
+        <v>2.92625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.74</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.607499999999999</v>
+        <v>-1.257499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.095</v>
+        <v>-0.17625</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.76125</v>
+        <v>-2.197499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.14</v>
+        <v>-0.165</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.65625</v>
+        <v>-2.201249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>0.32</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07999999999999999</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04749999999999943</v>
+        <v>-0.04749999999999899</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>0.41</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0725</v>
+        <v>-0.07250000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1774999999999998</v>
+        <v>-0.1774999999999993</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>0.59</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.045</v>
+        <v>-0.04500000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7862499999999999</v>
+        <v>0.7862500000000003</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.39</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01125</v>
+        <v>-0.01125000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>1.61375</v>
@@ -2026,7 +2026,7 @@
         <v>0.15</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09125000000000001</v>
+        <v>0.09125</v>
       </c>
       <c r="N13" t="n">
         <v>7.685</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4686</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4645</v>
+      </c>
+      <c r="E75" t="n">
+        <v>41</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-467</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-9.97%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-431</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-402</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.14625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.92625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.83206106870229</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.821501014198783</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
